--- a/data/trans_orig/P2C_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P2C_R-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2007</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2007 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>131725</t>
+          <t>131989</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>172959</t>
+          <t>173373</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>209090</t>
+          <t>205756</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>251441</t>
+          <t>250742</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>50,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>353804</t>
+          <t>351162</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>410585</t>
+          <t>408771</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>44,67%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>250144</t>
+          <t>249730</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>291378</t>
+          <t>291114</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>59,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>240593</t>
+          <t>241292</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>282944</t>
+          <t>286278</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>49,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>504552</t>
+          <t>506366</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>561333</t>
+          <t>563975</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,63%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>196051</t>
+          <t>197941</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>245398</t>
+          <t>245306</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>289667</t>
+          <t>290036</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>342601</t>
+          <t>341204</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>503204</t>
+          <t>503236</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>573735</t>
+          <t>573519</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,38%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>341111</t>
+          <t>341203</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>390458</t>
+          <t>388568</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>307561</t>
+          <t>308958</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>360495</t>
+          <t>360126</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>662936</t>
+          <t>663152</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>733467</t>
+          <t>733435</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>126720</t>
+          <t>126649</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>167144</t>
+          <t>166261</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>186830</t>
+          <t>186538</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>228326</t>
+          <t>229750</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>39,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>325415</t>
+          <t>323772</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>382543</t>
+          <t>380744</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>43,29%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>236237</t>
+          <t>237120</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>276661</t>
+          <t>276732</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>247779</t>
+          <t>246355</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>289275</t>
+          <t>289567</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>60,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>496943</t>
+          <t>498742</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>554071</t>
+          <t>555714</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>56,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>63,19%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>165839</t>
+          <t>167158</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>207465</t>
+          <t>208360</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>278412</t>
+          <t>280085</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>332050</t>
+          <t>329656</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>456836</t>
+          <t>460720</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>523075</t>
+          <t>525330</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>44,51%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>289767</t>
+          <t>288872</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>331393</t>
+          <t>330074</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>66,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>351012</t>
+          <t>353406</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>404650</t>
+          <t>402977</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>59,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>657219</t>
+          <t>654964</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>723458</t>
+          <t>719574</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>60,97%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>663183</t>
+          <t>666019</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>748468</t>
+          <t>749273</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1010970</t>
+          <t>1015276</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1103813</t>
+          <t>1109391</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1698885</t>
+          <t>1698777</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1829024</t>
+          <t>1830993</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>43,48%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1161758</t>
+          <t>1160953</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1247043</t>
+          <t>1244207</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>60,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1197549</t>
+          <t>1191971</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1290392</t>
+          <t>1286086</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>55,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2382564</t>
+          <t>2380595</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2512703</t>
+          <t>2512811</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2012</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2012 (tasa de respuesta: 99,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>193670</t>
+          <t>193495</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>237221</t>
+          <t>239360</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>282762</t>
+          <t>280389</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>326671</t>
+          <t>327196</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>54,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>63,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>485697</t>
+          <t>487913</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>552915</t>
+          <t>553151</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>56,04%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>235291</t>
+          <t>233152</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>278842</t>
+          <t>279017</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>59,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>187936</t>
+          <t>187411</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>231845</t>
+          <t>234218</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>434204</t>
+          <t>433968</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>501422</t>
+          <t>499206</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>50,57%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>300398</t>
+          <t>300386</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>351412</t>
+          <t>351738</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>53,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>439255</t>
+          <t>437349</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>491903</t>
+          <t>492260</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>58,81%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>65,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>752135</t>
+          <t>752010</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>827006</t>
+          <t>832552</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>59,11%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>310127</t>
+          <t>309801</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>361141</t>
+          <t>361153</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>254947</t>
+          <t>254590</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>307595</t>
+          <t>309501</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>581383</t>
+          <t>575837</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>656254</t>
+          <t>656379</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>210975</t>
+          <t>213044</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>256648</t>
+          <t>256978</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>334263</t>
+          <t>336093</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>381412</t>
+          <t>378903</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>63,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>559916</t>
+          <t>560625</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>626522</t>
+          <t>627684</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
+          <t>56,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,35%</t>
+          <t>63,47%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>200581</t>
+          <t>200251</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>246254</t>
+          <t>244185</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>53,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>150309</t>
+          <t>152818</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>197458</t>
+          <t>195628</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>362428</t>
+          <t>361266</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>429034</t>
+          <t>428325</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>43,31%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>252134</t>
+          <t>252581</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>300236</t>
+          <t>301997</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>396537</t>
+          <t>395872</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>452435</t>
+          <t>449695</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>54,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>62,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>668092</t>
+          <t>667988</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>737852</t>
+          <t>735175</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>57,9%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>245810</t>
+          <t>244049</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>293912</t>
+          <t>293465</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>53,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>271217</t>
+          <t>273957</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>327115</t>
+          <t>327780</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>531846</t>
+          <t>534523</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>601606</t>
+          <t>601710</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>47,39%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1006826</t>
+          <t>1006836</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1101905</t>
+          <t>1105466</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1502778</t>
+          <t>1497883</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1597594</t>
+          <t>1594913</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2530825</t>
+          <t>2525671</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2673145</t>
+          <t>2665308</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>57,27%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1035421</t>
+          <t>1031860</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1130500</t>
+          <t>1130490</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>919236</t>
+          <t>921917</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1014052</t>
+          <t>1018947</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1981011</t>
+          <t>1988848</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2123331</t>
+          <t>2128485</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,73%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2016</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2016 (tasa de respuesta: 94,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>161072</t>
+          <t>162018</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>202293</t>
+          <t>199174</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>185292</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>226500</t>
+          <t>226235</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>358917</t>
+          <t>357545</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>418968</t>
+          <t>415194</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>49,17%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>195668</t>
+          <t>198787</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>236889</t>
+          <t>235943</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,53%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>219968</t>
+          <t>220233</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>261176</t>
+          <t>263168</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>49,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>58,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>425461</t>
+          <t>429235</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>485512</t>
+          <t>486884</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>57,66%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>241811</t>
+          <t>239725</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>289473</t>
+          <t>289806</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>369075</t>
+          <t>366931</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>422394</t>
+          <t>420622</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>58,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>624455</t>
+          <t>623101</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>699342</t>
+          <t>697610</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>53,69%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>292860</t>
+          <t>292527</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>340522</t>
+          <t>342608</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>58,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>294620</t>
+          <t>296392</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>347939</t>
+          <t>350083</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>600005</t>
+          <t>601737</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>674892</t>
+          <t>676246</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>52,05%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>170914</t>
+          <t>169648</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>209844</t>
+          <t>211186</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>256991</t>
+          <t>257716</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>303268</t>
+          <t>303978</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>440276</t>
+          <t>438012</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>504640</t>
+          <t>501479</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>53,95%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>206313</t>
+          <t>204971</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>245243</t>
+          <t>246509</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>59,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>210046</t>
+          <t>209336</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>256323</t>
+          <t>255598</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>424831</t>
+          <t>427992</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>489195</t>
+          <t>491459</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>52,88%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>180694</t>
+          <t>183233</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>224502</t>
+          <t>223696</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>289548</t>
+          <t>289700</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>343070</t>
+          <t>343616</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>485520</t>
+          <t>482720</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>549041</t>
+          <t>553888</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>41,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>47,8%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>275975</t>
+          <t>276781</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>319783</t>
+          <t>317244</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,14%</t>
+          <t>55,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>63,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>315154</t>
+          <t>314608</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>368676</t>
+          <t>368524</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>609660</t>
+          <t>604813</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>673181</t>
+          <t>675981</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,1%</t>
+          <t>58,34%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>794075</t>
+          <t>797796</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>880538</t>
+          <t>881605</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1142237</t>
+          <t>1146440</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1246758</t>
+          <t>1247762</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1966355</t>
+          <t>1960395</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2099250</t>
+          <t>2097694</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>49,57%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1016390</t>
+          <t>1015323</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1102853</t>
+          <t>1099132</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1088262</t>
+          <t>1087258</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1192783</t>
+          <t>1188580</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2132698</t>
+          <t>2134254</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2265593</t>
+          <t>2271553</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>53,68%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2023</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>41336</t>
+          <t>42104</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>69996</t>
+          <t>70567</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>60448</t>
+          <t>61058</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>95913</t>
+          <t>94740</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>109744</t>
+          <t>110575</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>156667</t>
+          <t>157466</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>565445</t>
+          <t>564874</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>594105</t>
+          <t>593337</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>629417</t>
+          <t>630590</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>664882</t>
+          <t>664272</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1204105</t>
+          <t>1203306</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1251028</t>
+          <t>1250197</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,87%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>50134</t>
+          <t>50137</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>135755</t>
+          <t>133847</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>143150</t>
+          <t>141958</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>180456</t>
+          <t>181925</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>177066</t>
+          <t>177933</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>303830</t>
+          <t>305202</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,19%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1057109</t>
+          <t>1059017</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1142730</t>
+          <t>1142727</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>778195</t>
+          <t>776726</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>815501</t>
+          <t>816693</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1847686</t>
+          <t>1846314</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1974450</t>
+          <t>1973583</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,73%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32537</t>
+          <t>31975</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64158</t>
+          <t>60708</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>93805</t>
+          <t>93984</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>559972</t>
+          <t>602595</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>135752</t>
+          <t>133852</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>754224</t>
+          <t>749377</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>45,75%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>640522</t>
+          <t>643972</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>672143</t>
+          <t>672705</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>373394</t>
+          <t>330771</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>839561</t>
+          <t>839382</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>883822</t>
+          <t>888669</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1502294</t>
+          <t>1504194</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>54,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,83%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>54078</t>
+          <t>55103</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>83878</t>
+          <t>87531</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>72873</t>
+          <t>70543</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>111174</t>
+          <t>108859</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>137037</t>
+          <t>137504</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>184424</t>
+          <t>186512</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>842953</t>
+          <t>839300</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>872753</t>
+          <t>871728</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>983758</t>
+          <t>986073</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1022059</t>
+          <t>1024389</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1837339</t>
+          <t>1835251</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1884726</t>
+          <t>1884259</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,2%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>211217</t>
+          <t>209116</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>305947</t>
+          <t>305479</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>423866</t>
+          <t>422326</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1213729</t>
+          <t>1190097</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>678344</t>
+          <t>678095</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1552438</t>
+          <t>1452481</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>20,25%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3153870</t>
+          <t>3154338</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3248600</t>
+          <t>3250701</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2498551</t>
+          <t>2522183</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3288414</t>
+          <t>3289954</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5619659</t>
+          <t>5719616</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6493753</t>
+          <t>6494002</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,55%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2C_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P2C_R-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>131989</t>
+          <t>132325</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>173373</t>
+          <t>172133</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>205756</t>
+          <t>208927</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>250742</t>
+          <t>251502</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>51,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>351162</t>
+          <t>353145</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>408771</t>
+          <t>411247</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>44,94%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>249730</t>
+          <t>250970</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>291114</t>
+          <t>290778</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>241292</t>
+          <t>240532</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>286278</t>
+          <t>283107</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>506366</t>
+          <t>503890</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>563975</t>
+          <t>561992</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>61,41%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>197941</t>
+          <t>198694</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>245306</t>
+          <t>245690</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>290036</t>
+          <t>289755</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>341204</t>
+          <t>341563</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>52,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>503236</t>
+          <t>503625</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>573519</t>
+          <t>577258</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>46,68%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>341203</t>
+          <t>340819</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>388568</t>
+          <t>387815</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,25%</t>
+          <t>66,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>308958</t>
+          <t>308599</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>360126</t>
+          <t>360407</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>47,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>663152</t>
+          <t>659413</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>733435</t>
+          <t>733046</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>53,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>59,28%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>126649</t>
+          <t>125994</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>166261</t>
+          <t>164014</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>186538</t>
+          <t>187639</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>229750</t>
+          <t>231182</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>323772</t>
+          <t>322781</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>380744</t>
+          <t>382026</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>43,44%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>237120</t>
+          <t>239367</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>276732</t>
+          <t>277387</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,78%</t>
+          <t>59,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>68,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>246355</t>
+          <t>244923</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>289567</t>
+          <t>288466</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>51,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>498742</t>
+          <t>497460</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>555714</t>
+          <t>556705</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>63,3%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>167158</t>
+          <t>165049</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>208360</t>
+          <t>207666</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>280085</t>
+          <t>277610</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>329656</t>
+          <t>330091</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>460720</t>
+          <t>459063</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>525330</t>
+          <t>523723</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>44,37%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>288872</t>
+          <t>289566</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>330074</t>
+          <t>332183</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,1%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>353406</t>
+          <t>352971</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>402977</t>
+          <t>405452</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>654964</t>
+          <t>656571</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>719574</t>
+          <t>721231</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>55,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>61,11%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>666019</t>
+          <t>664139</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>749273</t>
+          <t>750667</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1015276</t>
+          <t>1014719</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1109391</t>
+          <t>1108578</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>44,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1698777</t>
+          <t>1695103</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1830993</t>
+          <t>1826314</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>43,36%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1160953</t>
+          <t>1159559</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1244207</t>
+          <t>1246087</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>60,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1191971</t>
+          <t>1192784</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1286086</t>
+          <t>1286643</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>51,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2380595</t>
+          <t>2385274</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2512811</t>
+          <t>2516485</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>59,75%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>193495</t>
+          <t>193756</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>239360</t>
+          <t>236372</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>50,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>280389</t>
+          <t>280885</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>327196</t>
+          <t>325467</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,49%</t>
+          <t>54,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,58%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>487913</t>
+          <t>483795</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>553151</t>
+          <t>549387</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>55,66%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>233152</t>
+          <t>236140</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>279017</t>
+          <t>278756</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>187411</t>
+          <t>189140</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>234218</t>
+          <t>233722</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>433968</t>
+          <t>437732</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>499206</t>
+          <t>503324</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>50,99%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>300386</t>
+          <t>300235</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>351738</t>
+          <t>351945</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>53,17%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>437349</t>
+          <t>438556</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>492260</t>
+          <t>494577</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>66,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>752010</t>
+          <t>755474</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>832552</t>
+          <t>832374</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>53,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>59,1%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>309801</t>
+          <t>309594</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>361153</t>
+          <t>361304</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>254590</t>
+          <t>252273</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>309501</t>
+          <t>308294</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>575837</t>
+          <t>576015</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>656379</t>
+          <t>652915</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>46,36%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>213044</t>
+          <t>213574</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>256978</t>
+          <t>258411</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>336093</t>
+          <t>333458</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>378903</t>
+          <t>381121</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>62,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>71,26%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>560625</t>
+          <t>559304</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>627684</t>
+          <t>624326</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>63,13%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>200251</t>
+          <t>198818</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>244185</t>
+          <t>243655</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>152818</t>
+          <t>150600</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>195628</t>
+          <t>198263</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>361266</t>
+          <t>364624</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>428325</t>
+          <t>429646</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>43,44%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>252581</t>
+          <t>253877</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>301997</t>
+          <t>302531</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>395872</t>
+          <t>393574</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>449695</t>
+          <t>447985</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>667988</t>
+          <t>665159</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>735175</t>
+          <t>737991</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>58,12%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>244049</t>
+          <t>243515</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>293465</t>
+          <t>292169</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>53,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>273957</t>
+          <t>275667</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>327780</t>
+          <t>330078</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>534523</t>
+          <t>531707</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>601710</t>
+          <t>604539</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>47,61%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1006836</t>
+          <t>1010607</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1105466</t>
+          <t>1101968</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,72%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1497883</t>
+          <t>1501790</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1594913</t>
+          <t>1599144</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>59,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,37%</t>
+          <t>63,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2525671</t>
+          <t>2535549</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2665308</t>
+          <t>2675987</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,27%</t>
+          <t>57,5%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1031860</t>
+          <t>1035358</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1130490</t>
+          <t>1126719</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>921917</t>
+          <t>917686</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1018947</t>
+          <t>1015040</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1988848</t>
+          <t>1978169</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2128485</t>
+          <t>2118607</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>45,52%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>162018</t>
+          <t>158888</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>199174</t>
+          <t>199955</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,05%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>185819</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>226235</t>
+          <t>227261</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>357545</t>
+          <t>357890</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>415194</t>
+          <t>415401</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>49,19%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>198787</t>
+          <t>198006</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>235943</t>
+          <t>239073</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>60,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>220233</t>
+          <t>219207</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>263168</t>
+          <t>260649</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>58,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>429235</t>
+          <t>429028</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>486884</t>
+          <t>486539</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>57,62%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>239725</t>
+          <t>240056</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>289806</t>
+          <t>290447</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,77%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>366931</t>
+          <t>366477</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>420622</t>
+          <t>422122</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>51,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>58,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>623101</t>
+          <t>626671</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>697610</t>
+          <t>696056</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>48,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>53,57%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>292527</t>
+          <t>291886</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>342608</t>
+          <t>342277</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>50,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>296392</t>
+          <t>294892</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>350083</t>
+          <t>350537</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>601737</t>
+          <t>603291</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>676246</t>
+          <t>672676</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>51,77%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>169648</t>
+          <t>170570</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>211186</t>
+          <t>211710</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>257716</t>
+          <t>257510</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>303978</t>
+          <t>302007</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>58,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>438012</t>
+          <t>438471</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>501479</t>
+          <t>503174</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>54,14%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>204971</t>
+          <t>204447</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>246509</t>
+          <t>245587</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>209336</t>
+          <t>211307</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>255598</t>
+          <t>255804</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>427992</t>
+          <t>426297</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>491459</t>
+          <t>491000</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>52,83%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>183233</t>
+          <t>180470</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>223696</t>
+          <t>222897</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,82 +5671,82 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>44,54%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>302</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>316287</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>291079</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>344016</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>48,05%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>44,22%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>52,26%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>501</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>517988</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>484825</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>553166</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
           <t>44,7%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>302</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>316287</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>289700</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>343616</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>48,05%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>44,01%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>52,2%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>501</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>517988</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>482720</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>553888</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>44,7%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>47,74%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>276781</t>
+          <t>277580</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>317244</t>
+          <t>320007</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,82 +5784,82 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>55,46%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>63,94%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>341937</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>314208</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>367145</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>51,95%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>47,74%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>55,78%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>606</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>640713</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>605535</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>673876</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
           <t>55,3%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>63,39%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>297</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>341937</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>314608</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>368524</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>51,95%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>47,8%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>55,99%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>606</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>640713</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>604813</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>675981</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>55,3%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>58,16%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>797796</t>
+          <t>800754</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>881605</t>
+          <t>881590</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1146440</t>
+          <t>1148280</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1247762</t>
+          <t>1246540</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1960395</t>
+          <t>1974561</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2097694</t>
+          <t>2109294</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>49,84%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1015323</t>
+          <t>1015338</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1099132</t>
+          <t>1096174</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>53,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1087258</t>
+          <t>1088480</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1188580</t>
+          <t>1186740</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2134254</t>
+          <t>2122654</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2271553</t>
+          <t>2257387</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>53,34%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>54926</t>
+          <t>59739</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42104</t>
+          <t>45587</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>70567</t>
+          <t>78082</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>78672</t>
+          <t>87139</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>61058</t>
+          <t>73247</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>94740</t>
+          <t>105910</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>133598</t>
+          <t>146878</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>110575</t>
+          <t>126685</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>157466</t>
+          <t>170838</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,99%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>580515</t>
+          <t>630971</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>564874</t>
+          <t>612628</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>593337</t>
+          <t>645123</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>646658</t>
+          <t>647041</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>630590</t>
+          <t>628270</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>664272</t>
+          <t>660933</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1227174</t>
+          <t>1278011</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1203306</t>
+          <t>1254051</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1250197</t>
+          <t>1298204</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,11%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>100174</t>
+          <t>123280</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>50137</t>
+          <t>101920</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>133847</t>
+          <t>148634</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>161039</t>
+          <t>184020</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>141958</t>
+          <t>162989</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>181925</t>
+          <t>207965</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>261213</t>
+          <t>307301</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>177933</t>
+          <t>272206</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>305202</t>
+          <t>337647</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>15,92%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1092690</t>
+          <t>925637</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1059017</t>
+          <t>900283</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1142727</t>
+          <t>946997</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>797612</t>
+          <t>887454</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>776726</t>
+          <t>863509</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>816693</t>
+          <t>908485</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1890303</t>
+          <t>1813090</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1846314</t>
+          <t>1782744</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1973583</t>
+          <t>1848185</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>87,16%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>44333</t>
+          <t>52912</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31975</t>
+          <t>39115</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>60708</t>
+          <t>73207</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>284333</t>
+          <t>97935</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>93984</t>
+          <t>80679</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>602595</t>
+          <t>116065</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>328665</t>
+          <t>150846</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>133852</t>
+          <t>125795</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>749377</t>
+          <t>176089</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>10,9%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>660347</t>
+          <t>750161</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>643972</t>
+          <t>729866</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>672705</t>
+          <t>763958</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>649033</t>
+          <t>714324</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>330771</t>
+          <t>696194</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>839382</t>
+          <t>731580</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1309381</t>
+          <t>1464486</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>888669</t>
+          <t>1439243</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1504194</t>
+          <t>1489537</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>92,21%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>68083</t>
+          <t>77309</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>55103</t>
+          <t>61959</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>87531</t>
+          <t>96042</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>93131</t>
+          <t>111544</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>70543</t>
+          <t>95836</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>108859</t>
+          <t>131676</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>161214</t>
+          <t>188854</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>137504</t>
+          <t>165691</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>186512</t>
+          <t>212412</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>858748</t>
+          <t>912753</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>839300</t>
+          <t>894020</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>871728</t>
+          <t>928103</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1001801</t>
+          <t>1007497</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>986073</t>
+          <t>987365</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1024389</t>
+          <t>1023205</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1860549</t>
+          <t>1920250</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1835251</t>
+          <t>1896692</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1884259</t>
+          <t>1943413</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>92,14%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>267516</t>
+          <t>313239</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>209116</t>
+          <t>280385</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>305479</t>
+          <t>350896</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>617174</t>
+          <t>480638</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>422326</t>
+          <t>439680</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1190097</t>
+          <t>517265</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>884690</t>
+          <t>793878</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>678095</t>
+          <t>743311</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1452481</t>
+          <t>849666</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>11,69%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3192301</t>
+          <t>3219523</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3154338</t>
+          <t>3181866</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3250701</t>
+          <t>3252377</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3095106</t>
+          <t>3256316</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2522183</t>
+          <t>3219689</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3289954</t>
+          <t>3297274</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6287407</t>
+          <t>6475838</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5719616</t>
+          <t>6420050</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6494002</t>
+          <t>6526405</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>89,78%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">

--- a/data/trans_orig/P2C_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P2C_R-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2007 (tasa de respuesta: 99,95%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2007 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2012 (tasa de respuesta: 99,27%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2012 (tasa de respuesta: 99,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2016 (tasa de respuesta: 94,57%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2016 (tasa de respuesta: 94,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
